--- a/Decks/Rani.xlsx
+++ b/Decks/Rani.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\Magic\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96AB74ED-9659-44AD-99EE-03C810412AD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16953DF8-CFC6-48D9-81B5-5E311CDC1435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{858CA34D-E376-4636-8523-98EF52C57444}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{858CA34D-E376-4636-8523-98EF52C57444}"/>
   </bookViews>
   <sheets>
     <sheet name="Rani" sheetId="1" r:id="rId1"/>
@@ -65,9 +65,6 @@
     <t>Terreno</t>
   </si>
   <si>
-    <t>Emergency Zone</t>
-  </si>
-  <si>
     <t>Rogue's Passage</t>
   </si>
   <si>
@@ -296,9 +293,6 @@
     <t>Magda, the Hoardmaster</t>
   </si>
   <si>
-    <t>Royalty Assassin</t>
-  </si>
-  <si>
     <t>Waterbender's Restoration</t>
   </si>
   <si>
@@ -342,6 +336,12 @@
   </si>
   <si>
     <t>Coercive Impetus</t>
+  </si>
+  <si>
+    <t>Emergence Zone</t>
+  </si>
+  <si>
+    <t>Royal Assassin</t>
   </si>
 </sst>
 </file>
@@ -786,10 +786,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -801,10 +801,10 @@
         <v>0</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -816,10 +816,10 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -831,10 +831,10 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -861,10 +861,10 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -876,10 +876,10 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -891,10 +891,10 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -906,10 +906,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -921,10 +921,10 @@
         <v>1</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" t="s">
         <v>19</v>
-      </c>
-      <c r="D12" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -936,10 +936,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" t="s">
         <v>21</v>
-      </c>
-      <c r="D13" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>0</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -996,10 +996,10 @@
         <v>1</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1011,10 +1011,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1026,10 +1026,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1041,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1056,10 +1056,10 @@
         <v>0</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1071,10 +1071,10 @@
         <v>0</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1086,10 +1086,10 @@
         <v>0</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1101,10 +1101,10 @@
         <v>0</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1116,10 +1116,10 @@
         <v>0</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1131,10 +1131,10 @@
         <v>0</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1146,10 +1146,10 @@
         <v>0</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1161,10 +1161,10 @@
         <v>0</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1176,10 +1176,10 @@
         <v>0</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1191,10 +1191,10 @@
         <v>0</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1206,10 +1206,10 @@
         <v>0</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1221,10 +1221,10 @@
         <v>0</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1236,10 +1236,10 @@
         <v>0</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1251,10 +1251,10 @@
         <v>0</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1266,10 +1266,10 @@
         <v>0</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1281,10 +1281,10 @@
         <v>0</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1296,10 +1296,10 @@
         <v>0</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D37" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1311,10 +1311,10 @@
         <v>0</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D39" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1341,953 +1341,953 @@
         <v>0</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>29</v>
+      </c>
+      <c r="B41" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B41" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="D41" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B42" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B43" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D43" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B44" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D44" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B45" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C45" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D45" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B46" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D46" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B47" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D47" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F47"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B48" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D48" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B49" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B50" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C51" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B51" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>42</v>
-      </c>
       <c r="D51" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D52" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D53" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F53"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D54" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D55" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D56" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C57" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D57" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D58" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>48</v>
+      </c>
+      <c r="B59" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C59" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B59" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>50</v>
-      </c>
       <c r="D59" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F59"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B60" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D60" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F60"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D61" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F61"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B62" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D62" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F62"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B63" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D63" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F63"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D64" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D65" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F65"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B66" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D66" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F66"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B67" s="5" t="b">
         <f t="shared" ref="B67:B101" si="1">C67&lt;&gt;D67</f>
         <v>0</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D67" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F67"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B68" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D68" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F68"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D69" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F69"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D70" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F70"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D71" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F71" s="4"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D72" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F72" s="4"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D73" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F73" s="4"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D74" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D75" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D76" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D77" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D78" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B79" s="5" t="b">
         <f>C79&lt;&gt;D79</f>
         <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D79" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F79"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D80" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F80"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C81" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D81" t="s">
         <v>72</v>
-      </c>
-      <c r="D81" t="s">
-        <v>73</v>
       </c>
       <c r="F81"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E82" s="4"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D83" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D84" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>77</v>
+      </c>
+      <c r="B85" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D85" t="s">
         <v>78</v>
-      </c>
-      <c r="B85" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D85" t="s">
-        <v>79</v>
       </c>
       <c r="E85" s="4"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D86" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D87" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F87" s="4"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D88" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F88" s="4"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D89" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F89" s="4"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D90" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F90" s="4"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D91" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F91" s="4"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D92" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D93" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D95" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F95"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D96" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F96"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D97" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D98" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Rani.xlsx
+++ b/Decks/Rani.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16953DF8-CFC6-48D9-81B5-5E311CDC1435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28E6D641-D62C-4314-A755-64452C9097A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{858CA34D-E376-4636-8523-98EF52C57444}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{858CA34D-E376-4636-8523-98EF52C57444}"/>
   </bookViews>
   <sheets>
     <sheet name="Rani" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="98">
   <si>
     <t>Função</t>
   </si>
@@ -92,9 +92,6 @@
     <t>Bojuka Bog</t>
   </si>
   <si>
-    <t>Dreadship Reef</t>
-  </si>
-  <si>
     <t>Reliquary Tower</t>
   </si>
   <si>
@@ -254,21 +251,12 @@
     <t>Shiny Impetus</t>
   </si>
   <si>
-    <t>Bothersome Quasit</t>
-  </si>
-  <si>
     <t>Goblin Spymaster</t>
   </si>
   <si>
-    <t>Coronation of Chaos</t>
-  </si>
-  <si>
     <t>Ghoulish Impetus</t>
   </si>
   <si>
-    <t>Geode Rager</t>
-  </si>
-  <si>
     <t>Suporte</t>
   </si>
   <si>
@@ -293,9 +281,6 @@
     <t>Magda, the Hoardmaster</t>
   </si>
   <si>
-    <t>Waterbender's Restoration</t>
-  </si>
-  <si>
     <t>Revenge of Ravens</t>
   </si>
   <si>
@@ -314,9 +299,6 @@
     <t>Curse of Verbosity</t>
   </si>
   <si>
-    <t>Komainu Battle Armor</t>
-  </si>
-  <si>
     <t>Powerbalance</t>
   </si>
   <si>
@@ -326,9 +308,6 @@
     <t>Baeloth Barrityl, Entertainer</t>
   </si>
   <si>
-    <t>Evolving Wilds</t>
-  </si>
-  <si>
     <t>Fast Forward</t>
   </si>
   <si>
@@ -338,10 +317,19 @@
     <t>Coercive Impetus</t>
   </si>
   <si>
-    <t>Emergence Zone</t>
-  </si>
-  <si>
-    <t>Royal Assassin</t>
+    <t>Heaven Sent</t>
+  </si>
+  <si>
+    <t>Loki, God of Mischief</t>
+  </si>
+  <si>
+    <t>Kang Dynasty</t>
+  </si>
+  <si>
+    <t>Puppet Master, String Puller</t>
+  </si>
+  <si>
+    <t>Archnemesis</t>
   </si>
 </sst>
 </file>
@@ -782,11 +770,11 @@
         <v>8</v>
       </c>
       <c r="B3" s="5" t="b">
-        <f t="shared" ref="B3:B66" si="0">C3&lt;&gt;D3</f>
-        <v>1</v>
+        <f t="shared" ref="B3:B67" si="0">C3&lt;&gt;D3</f>
+        <v>0</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>96</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
@@ -918,13 +906,13 @@
       </c>
       <c r="B12" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -936,10 +924,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
         <v>20</v>
-      </c>
-      <c r="D13" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -951,10 +939,10 @@
         <v>0</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -966,10 +954,10 @@
         <v>0</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -981,10 +969,10 @@
         <v>0</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -993,13 +981,13 @@
       </c>
       <c r="B17" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="D17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1011,10 +999,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D18" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1026,10 +1014,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1041,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1056,10 +1044,10 @@
         <v>0</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1071,10 +1059,10 @@
         <v>0</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1086,10 +1074,10 @@
         <v>0</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1101,10 +1089,10 @@
         <v>0</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1116,10 +1104,10 @@
         <v>0</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1131,10 +1119,10 @@
         <v>0</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1146,10 +1134,10 @@
         <v>0</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1161,10 +1149,10 @@
         <v>0</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1176,10 +1164,10 @@
         <v>0</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1191,10 +1179,10 @@
         <v>0</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1206,10 +1194,10 @@
         <v>0</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1221,10 +1209,10 @@
         <v>0</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1236,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1251,10 +1239,10 @@
         <v>0</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1266,10 +1254,10 @@
         <v>0</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1281,10 +1269,10 @@
         <v>0</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1296,10 +1284,10 @@
         <v>0</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1311,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1326,10 +1314,10 @@
         <v>0</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1341,953 +1329,953 @@
         <v>0</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>28</v>
+      </c>
+      <c r="B41" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B41" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="D41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B42" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D42" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B43" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B44" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D44" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B45" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C45" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D45" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B46" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D46" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B47" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D47" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F47"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B48" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D48" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B49" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B50" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C51" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B51" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="D51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B52" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D52" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B53" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D53" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F53"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B54" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D54" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B55" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D55" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B56" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>C56&lt;&gt;D56</f>
+        <v>1</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D56" t="s">
-        <v>45</v>
+        <v>87</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B57" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C57" t="s">
-        <v>46</v>
+      <c r="C57" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="D57" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B58" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C58" s="4" t="s">
-        <v>47</v>
+      <c r="C58" t="s">
+        <v>45</v>
       </c>
       <c r="D58" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B59" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D59" t="s">
-        <v>49</v>
-      </c>
-      <c r="F59"/>
+        <v>46</v>
+      </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>47</v>
+      </c>
+      <c r="B60" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C60" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B60" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>50</v>
-      </c>
       <c r="D60" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F60"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D61" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F61"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B62" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D62" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F62"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B63" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D63" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F63"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D64" t="s">
-        <v>54</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="F64"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D65" t="s">
-        <v>55</v>
-      </c>
-      <c r="F65"/>
+        <v>53</v>
+      </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B66" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D66" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F66"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B67" s="5" t="b">
-        <f t="shared" ref="B67:B101" si="1">C67&lt;&gt;D67</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D67" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F67"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>56</v>
+      </c>
+      <c r="B68" s="5" t="b">
+        <f t="shared" ref="B68:B101" si="1">C68&lt;&gt;D68</f>
+        <v>0</v>
+      </c>
+      <c r="C68" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B68" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>59</v>
-      </c>
       <c r="D68" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F68"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D69" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F69"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D70" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F70"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D71" t="s">
-        <v>62</v>
-      </c>
-      <c r="F71" s="4"/>
+        <v>60</v>
+      </c>
+      <c r="F71"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D72" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F72" s="4"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D73" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F73" s="4"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D74" t="s">
-        <v>65</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="F74" s="4"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D75" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D76" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D77" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D78" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B79" s="5" t="b">
-        <f>C79&lt;&gt;D79</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="D79" t="s">
-        <v>97</v>
-      </c>
-      <c r="F79"/>
+        <v>68</v>
+      </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B80" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C80&lt;&gt;D80</f>
         <v>0</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="D80" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F80"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D81" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F81"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E82" s="4"/>
+        <v>96</v>
+      </c>
+      <c r="D82" t="s">
+        <v>96</v>
+      </c>
+      <c r="F82"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D83" t="s">
-        <v>75</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E83" s="4"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D84" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="D85" t="s">
-        <v>78</v>
-      </c>
-      <c r="E85" s="4"/>
+        <v>95</v>
+      </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D86" t="s">
-        <v>79</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="E86" s="4"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D87" t="s">
-        <v>80</v>
-      </c>
-      <c r="F87" s="4"/>
+        <v>75</v>
+      </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D88" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F88" s="4"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>73</v>
+      </c>
+      <c r="B89" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C89" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B89" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>82</v>
-      </c>
       <c r="D89" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F89" s="4"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D90" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F90" s="4"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D91" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F91" s="4"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="D92" t="s">
-        <v>85</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="F92" s="4"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="D93" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D94" s="4" t="s">
-        <v>87</v>
+        <v>81</v>
+      </c>
+      <c r="D94" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D95" t="s">
-        <v>88</v>
-      </c>
-      <c r="F95"/>
+        <v>82</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D96" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F96"/>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D97" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+      <c r="F97"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D98" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D99" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+      <c r="D99" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
